--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,6 +1622,573 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123326129</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Visjön, Igelfors, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>545596</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6522617</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123326307</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Visjön, Igelfors, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>545693</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6522649</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123326291</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Visjön, Igelfors, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>545653</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6522620</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123326310</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Visjön, Igelfors, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>545680</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6522666</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123326300</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Visjön, Igelfors, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>545678</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6522628</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298795</v>
+        <v>123298799</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545679</v>
+        <v>545593</v>
       </c>
       <c r="R2" t="n">
-        <v>6522615</v>
+        <v>6522623</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298793</v>
+        <v>123298794</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,32 +789,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
@@ -859,18 +863,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298790</v>
+        <v>123299964</v>
       </c>
       <c r="B4" t="n">
-        <v>91640</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,37 +903,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545705</v>
+        <v>545682</v>
       </c>
       <c r="R4" t="n">
-        <v>6522653</v>
+        <v>6522616</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,17 +990,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298794</v>
+        <v>123298791</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,46 +1009,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545664</v>
+        <v>545692</v>
       </c>
       <c r="R5" t="n">
-        <v>6522623</v>
+        <v>6522648</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,6 +1085,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298791</v>
+        <v>123298790</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>91643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,42 +1116,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545692</v>
+        <v>545705</v>
       </c>
       <c r="R6" t="n">
-        <v>6522648</v>
+        <v>6522653</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,7 +1188,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,7 +1209,7 @@
         <v>123298798</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298797</v>
+        <v>123298793</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,38 +1320,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545605</v>
+        <v>545664</v>
       </c>
       <c r="R8" t="n">
-        <v>6522652</v>
+        <v>6522623</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,12 +1390,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1412,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298799</v>
+        <v>123298797</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>92236</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,25 +1432,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545593</v>
+        <v>545605</v>
       </c>
       <c r="R9" t="n">
-        <v>6522623</v>
+        <v>6522652</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1514,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299964</v>
+        <v>123298795</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>90955</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,49 +1534,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545682</v>
+        <v>545679</v>
       </c>
       <c r="R10" t="n">
-        <v>6522616</v>
+        <v>6522615</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326129</v>
+        <v>123326310</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,30 +1636,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1667,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545596</v>
+        <v>545680</v>
       </c>
       <c r="R11" t="n">
-        <v>6522617</v>
+        <v>6522666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326307</v>
+        <v>123326300</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,39 +1751,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545693</v>
+        <v>545678</v>
       </c>
       <c r="R12" t="n">
-        <v>6522649</v>
+        <v>6522628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,11 +1818,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326291</v>
+        <v>123326307</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,7 +1880,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545653</v>
+        <v>545693</v>
       </c>
       <c r="R13" t="n">
-        <v>6522620</v>
+        <v>6522649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123326310</v>
+        <v>123326291</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,7 +2000,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2022,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545680</v>
+        <v>545653</v>
       </c>
       <c r="R14" t="n">
-        <v>6522666</v>
+        <v>6522620</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,6 +2053,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123326300</v>
+        <v>123326129</v>
       </c>
       <c r="B15" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545678</v>
+        <v>545596</v>
       </c>
       <c r="R15" t="n">
-        <v>6522628</v>
+        <v>6522617</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298799</v>
+        <v>123298794</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545593</v>
+        <v>545664</v>
       </c>
       <c r="R2" t="n">
         <v>6522623</v>
@@ -777,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298794</v>
+        <v>123298797</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>92238</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545664</v>
+        <v>545605</v>
       </c>
       <c r="R3" t="n">
-        <v>6522623</v>
+        <v>6522652</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298791</v>
+        <v>123298798</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,42 +1009,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545692</v>
+        <v>545584</v>
       </c>
       <c r="R5" t="n">
-        <v>6522648</v>
+        <v>6522641</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,7 +1081,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298790</v>
+        <v>123298795</v>
       </c>
       <c r="B6" t="n">
-        <v>91643</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545705</v>
+        <v>545679</v>
       </c>
       <c r="R6" t="n">
-        <v>6522653</v>
+        <v>6522615</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298798</v>
+        <v>123298793</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,38 +1213,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545584</v>
+        <v>545664</v>
       </c>
       <c r="R7" t="n">
-        <v>6522641</v>
+        <v>6522623</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1284,12 +1283,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1308,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298793</v>
+        <v>123298799</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1320,39 +1325,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545664</v>
+        <v>545593</v>
       </c>
       <c r="R8" t="n">
         <v>6522623</v>
@@ -1390,18 +1391,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1420,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298797</v>
+        <v>123298790</v>
       </c>
       <c r="B9" t="n">
-        <v>92236</v>
+        <v>91645</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545605</v>
+        <v>545705</v>
       </c>
       <c r="R9" t="n">
-        <v>6522652</v>
+        <v>6522653</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1522,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298795</v>
+        <v>123298791</v>
       </c>
       <c r="B10" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,38 +1529,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545679</v>
+        <v>545692</v>
       </c>
       <c r="R10" t="n">
-        <v>6522615</v>
+        <v>6522648</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,6 +1605,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326310</v>
+        <v>123326300</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,39 +1636,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1676,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545680</v>
+        <v>545678</v>
       </c>
       <c r="R11" t="n">
-        <v>6522666</v>
+        <v>6522628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326300</v>
+        <v>123326129</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545678</v>
+        <v>545596</v>
       </c>
       <c r="R12" t="n">
-        <v>6522628</v>
+        <v>6522617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326307</v>
+        <v>123326291</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,7 +1871,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1897,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545693</v>
+        <v>545653</v>
       </c>
       <c r="R13" t="n">
-        <v>6522649</v>
+        <v>6522620</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123326291</v>
+        <v>123326307</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2000,7 +1991,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2017,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545653</v>
+        <v>545693</v>
       </c>
       <c r="R14" t="n">
-        <v>6522620</v>
+        <v>6522649</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123326129</v>
+        <v>123326310</v>
       </c>
       <c r="B15" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,30 +2088,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545596</v>
+        <v>545680</v>
       </c>
       <c r="R15" t="n">
-        <v>6522617</v>
+        <v>6522666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298794</v>
+        <v>123298799</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>90963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545664</v>
+        <v>545593</v>
       </c>
       <c r="R2" t="n">
         <v>6522623</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298797</v>
+        <v>123298793</v>
       </c>
       <c r="B3" t="n">
-        <v>92238</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545605</v>
+        <v>545664</v>
       </c>
       <c r="R3" t="n">
-        <v>6522652</v>
+        <v>6522623</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -863,12 +859,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299964</v>
+        <v>123298798</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>90963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,49 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545682</v>
+        <v>545584</v>
       </c>
       <c r="R4" t="n">
-        <v>6522616</v>
+        <v>6522641</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,17 +984,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298798</v>
+        <v>123298795</v>
       </c>
       <c r="B5" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545584</v>
+        <v>545679</v>
       </c>
       <c r="R5" t="n">
-        <v>6522641</v>
+        <v>6522615</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298795</v>
+        <v>123298791</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1105,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545679</v>
+        <v>545692</v>
       </c>
       <c r="R6" t="n">
-        <v>6522615</v>
+        <v>6522648</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1201,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298793</v>
+        <v>123299964</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1213,45 +1212,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545664</v>
+        <v>545682</v>
       </c>
       <c r="R7" t="n">
-        <v>6522623</v>
+        <v>6522616</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,18 +1286,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1306,17 +1303,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298799</v>
+        <v>123298797</v>
       </c>
       <c r="B8" t="n">
-        <v>90957</v>
+        <v>92244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1322,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545593</v>
+        <v>545605</v>
       </c>
       <c r="R8" t="n">
-        <v>6522623</v>
+        <v>6522652</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1418,7 +1415,7 @@
         <v>123298790</v>
       </c>
       <c r="B9" t="n">
-        <v>91645</v>
+        <v>91651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298791</v>
+        <v>123298794</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,42 +1526,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545692</v>
+        <v>545664</v>
       </c>
       <c r="R10" t="n">
-        <v>6522648</v>
+        <v>6522623</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,7 +1606,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326300</v>
+        <v>123326310</v>
       </c>
       <c r="B11" t="n">
-        <v>90957</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,30 +1636,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1667,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545678</v>
+        <v>545680</v>
       </c>
       <c r="R11" t="n">
-        <v>6522628</v>
+        <v>6522666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326129</v>
+        <v>123326300</v>
       </c>
       <c r="B12" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545596</v>
+        <v>545678</v>
       </c>
       <c r="R12" t="n">
-        <v>6522617</v>
+        <v>6522628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326291</v>
+        <v>123326129</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,39 +1857,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545653</v>
+        <v>545596</v>
       </c>
       <c r="R13" t="n">
-        <v>6522620</v>
+        <v>6522617</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,11 +1924,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1954,7 @@
         <v>123326307</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123326310</v>
+        <v>123326291</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,7 +2106,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2128,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545680</v>
+        <v>545653</v>
       </c>
       <c r="R15" t="n">
-        <v>6522666</v>
+        <v>6522620</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,6 +2159,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298799</v>
+        <v>123298798</v>
       </c>
       <c r="B2" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545593</v>
+        <v>545584</v>
       </c>
       <c r="R2" t="n">
-        <v>6522623</v>
+        <v>6522641</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298793</v>
+        <v>123298799</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>90966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,39 +789,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545664</v>
+        <v>545593</v>
       </c>
       <c r="R3" t="n">
         <v>6522623</v>
@@ -859,18 +855,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298798</v>
+        <v>123298797</v>
       </c>
       <c r="B4" t="n">
-        <v>90963</v>
+        <v>92247</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545584</v>
+        <v>545605</v>
       </c>
       <c r="R4" t="n">
-        <v>6522641</v>
+        <v>6522652</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298795</v>
+        <v>123298790</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>91654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545679</v>
+        <v>545705</v>
       </c>
       <c r="R5" t="n">
-        <v>6522615</v>
+        <v>6522653</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1096,7 +1086,7 @@
         <v>123298791</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299964</v>
+        <v>123298795</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>90966</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,49 +1202,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545682</v>
+        <v>545679</v>
       </c>
       <c r="R7" t="n">
-        <v>6522616</v>
+        <v>6522615</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,17 +1285,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298797</v>
+        <v>123299964</v>
       </c>
       <c r="B8" t="n">
-        <v>92244</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,37 +1308,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545605</v>
+        <v>545682</v>
       </c>
       <c r="R8" t="n">
-        <v>6522652</v>
+        <v>6522616</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,17 +1395,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298790</v>
+        <v>123298793</v>
       </c>
       <c r="B9" t="n">
-        <v>91651</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,38 +1414,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545705</v>
+        <v>545664</v>
       </c>
       <c r="R9" t="n">
-        <v>6522653</v>
+        <v>6522623</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1490,12 +1484,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326310</v>
+        <v>123326300</v>
       </c>
       <c r="B11" t="n">
-        <v>98376</v>
+        <v>90966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,39 +1636,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1676,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545680</v>
+        <v>545678</v>
       </c>
       <c r="R11" t="n">
-        <v>6522666</v>
+        <v>6522628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326300</v>
+        <v>123326129</v>
       </c>
       <c r="B12" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545678</v>
+        <v>545596</v>
       </c>
       <c r="R12" t="n">
-        <v>6522628</v>
+        <v>6522617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326129</v>
+        <v>123326307</v>
       </c>
       <c r="B13" t="n">
-        <v>90963</v>
+        <v>98379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,30 +1848,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545596</v>
+        <v>545693</v>
       </c>
       <c r="R13" t="n">
-        <v>6522617</v>
+        <v>6522649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,6 +1924,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123326307</v>
+        <v>123326310</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,7 +1991,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2003,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545693</v>
+        <v>545680</v>
       </c>
       <c r="R14" t="n">
-        <v>6522649</v>
+        <v>6522666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,11 +2044,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,7 +2074,7 @@
         <v>123326291</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298790</v>
+        <v>123298791</v>
       </c>
       <c r="B5" t="n">
-        <v>91654</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545705</v>
+        <v>545692</v>
       </c>
       <c r="R5" t="n">
-        <v>6522653</v>
+        <v>6522648</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1065,6 +1069,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298791</v>
+        <v>123298790</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>91654</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,42 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545692</v>
+        <v>545705</v>
       </c>
       <c r="R6" t="n">
-        <v>6522648</v>
+        <v>6522653</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1171,7 +1172,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298798</v>
+        <v>123298797</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>92264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545584</v>
+        <v>545605</v>
       </c>
       <c r="R2" t="n">
-        <v>6522641</v>
+        <v>6522652</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298799</v>
+        <v>123298798</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545593</v>
+        <v>545584</v>
       </c>
       <c r="R3" t="n">
-        <v>6522623</v>
+        <v>6522641</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298797</v>
+        <v>123298795</v>
       </c>
       <c r="B4" t="n">
-        <v>92247</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545605</v>
+        <v>545679</v>
       </c>
       <c r="R4" t="n">
-        <v>6522652</v>
+        <v>6522615</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298791</v>
+        <v>123298799</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,42 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545692</v>
+        <v>545593</v>
       </c>
       <c r="R5" t="n">
-        <v>6522648</v>
+        <v>6522623</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1069,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1091,7 +1086,7 @@
         <v>123298790</v>
       </c>
       <c r="B6" t="n">
-        <v>91654</v>
+        <v>91671</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298795</v>
+        <v>123298793</v>
       </c>
       <c r="B7" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,38 +1197,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545679</v>
+        <v>545664</v>
       </c>
       <c r="R7" t="n">
-        <v>6522615</v>
+        <v>6522623</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1268,12 +1267,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298793</v>
+        <v>123298791</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,7 +1332,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1336,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545664</v>
+        <v>545692</v>
       </c>
       <c r="R8" t="n">
-        <v>6522623</v>
+        <v>6522648</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1372,11 +1377,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123326300</v>
+        <v>123326310</v>
       </c>
       <c r="B9" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,30 +1416,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1447,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545678</v>
+        <v>545680</v>
       </c>
       <c r="R9" t="n">
-        <v>6522628</v>
+        <v>6522666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123326129</v>
+        <v>123326291</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,30 +1531,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1553,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545596</v>
+        <v>545653</v>
       </c>
       <c r="R10" t="n">
-        <v>6522617</v>
+        <v>6522620</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,6 +1607,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326307</v>
+        <v>123326129</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,39 +1651,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1668,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545693</v>
+        <v>545596</v>
       </c>
       <c r="R11" t="n">
-        <v>6522649</v>
+        <v>6522617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1718,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326310</v>
+        <v>123326300</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,39 +1757,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545680</v>
+        <v>545678</v>
       </c>
       <c r="R12" t="n">
-        <v>6522666</v>
+        <v>6522628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326291</v>
+        <v>123326307</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545653</v>
+        <v>545693</v>
       </c>
       <c r="R13" t="n">
-        <v>6522620</v>
+        <v>6522649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,7 +1974,7 @@
         <v>123298794</v>
       </c>
       <c r="B14" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>123299964</v>
       </c>
       <c r="B15" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298797</v>
+        <v>123298790</v>
       </c>
       <c r="B2" t="n">
-        <v>92264</v>
+        <v>91676</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545605</v>
+        <v>545705</v>
       </c>
       <c r="R2" t="n">
-        <v>6522652</v>
+        <v>6522653</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298798</v>
+        <v>123298795</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545584</v>
+        <v>545679</v>
       </c>
       <c r="R3" t="n">
-        <v>6522641</v>
+        <v>6522615</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298795</v>
+        <v>123298797</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>92269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545679</v>
+        <v>545605</v>
       </c>
       <c r="R4" t="n">
-        <v>6522615</v>
+        <v>6522652</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298799</v>
+        <v>123298798</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545593</v>
+        <v>545584</v>
       </c>
       <c r="R5" t="n">
-        <v>6522623</v>
+        <v>6522641</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298790</v>
+        <v>123298799</v>
       </c>
       <c r="B6" t="n">
-        <v>91671</v>
+        <v>90988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545705</v>
+        <v>545593</v>
       </c>
       <c r="R6" t="n">
-        <v>6522653</v>
+        <v>6522623</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298793</v>
+        <v>123298791</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545664</v>
+        <v>545692</v>
       </c>
       <c r="R7" t="n">
-        <v>6522623</v>
+        <v>6522648</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1265,11 +1265,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298791</v>
+        <v>123298793</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,7 +1327,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1341,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545692</v>
+        <v>545664</v>
       </c>
       <c r="R8" t="n">
-        <v>6522648</v>
+        <v>6522623</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,6 +1372,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123326310</v>
+        <v>123326300</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,39 +1416,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1456,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545680</v>
+        <v>545678</v>
       </c>
       <c r="R9" t="n">
-        <v>6522666</v>
+        <v>6522628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123326291</v>
+        <v>123326307</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,7 +1545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1571,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545653</v>
+        <v>545693</v>
       </c>
       <c r="R10" t="n">
-        <v>6522620</v>
+        <v>6522649</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326129</v>
+        <v>123326291</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,30 +1642,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545596</v>
+        <v>545653</v>
       </c>
       <c r="R11" t="n">
-        <v>6522617</v>
+        <v>6522620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,6 +1718,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326300</v>
+        <v>123326129</v>
       </c>
       <c r="B12" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545678</v>
+        <v>545596</v>
       </c>
       <c r="R12" t="n">
-        <v>6522628</v>
+        <v>6522617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326307</v>
+        <v>123326310</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,7 +1891,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1903,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545693</v>
+        <v>545680</v>
       </c>
       <c r="R13" t="n">
-        <v>6522649</v>
+        <v>6522666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,11 +1944,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298794</v>
+        <v>123299964</v>
       </c>
       <c r="B14" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545664</v>
+        <v>545682</v>
       </c>
       <c r="R14" t="n">
-        <v>6522623</v>
+        <v>6522616</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,17 +2074,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123299964</v>
+        <v>123298794</v>
       </c>
       <c r="B15" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545682</v>
+        <v>545664</v>
       </c>
       <c r="R15" t="n">
-        <v>6522616</v>
+        <v>6522623</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298790</v>
+        <v>123298798</v>
       </c>
       <c r="B2" t="n">
-        <v>91676</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545705</v>
+        <v>545584</v>
       </c>
       <c r="R2" t="n">
-        <v>6522653</v>
+        <v>6522641</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298795</v>
+        <v>123298793</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545679</v>
+        <v>545664</v>
       </c>
       <c r="R3" t="n">
-        <v>6522615</v>
+        <v>6522623</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,12 +859,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298797</v>
+        <v>123298790</v>
       </c>
       <c r="B4" t="n">
-        <v>92269</v>
+        <v>91678</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545605</v>
+        <v>545705</v>
       </c>
       <c r="R4" t="n">
-        <v>6522652</v>
+        <v>6522653</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298798</v>
+        <v>123298797</v>
       </c>
       <c r="B5" t="n">
-        <v>90988</v>
+        <v>92271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545584</v>
+        <v>545605</v>
       </c>
       <c r="R5" t="n">
-        <v>6522641</v>
+        <v>6522652</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1096,7 @@
         <v>123298799</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,7 +1198,7 @@
         <v>123298791</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298793</v>
+        <v>123298795</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,42 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545664</v>
+        <v>545679</v>
       </c>
       <c r="R8" t="n">
-        <v>6522623</v>
+        <v>6522615</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1374,18 +1380,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123326300</v>
+        <v>123326307</v>
       </c>
       <c r="B9" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,30 +1416,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1447,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545678</v>
+        <v>545693</v>
       </c>
       <c r="R9" t="n">
-        <v>6522628</v>
+        <v>6522649</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,6 +1492,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123326307</v>
+        <v>123326300</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,39 +1536,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545693</v>
+        <v>545678</v>
       </c>
       <c r="R10" t="n">
-        <v>6522649</v>
+        <v>6522628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,11 +1603,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326291</v>
+        <v>123326310</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545653</v>
+        <v>545680</v>
       </c>
       <c r="R11" t="n">
-        <v>6522620</v>
+        <v>6522666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,11 +1718,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,7 +1748,7 @@
         <v>123326129</v>
       </c>
       <c r="B12" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326310</v>
+        <v>123326291</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,7 +1886,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1908,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545680</v>
+        <v>545653</v>
       </c>
       <c r="R13" t="n">
-        <v>6522666</v>
+        <v>6522620</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,6 +1939,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298791</v>
+        <v>123298795</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,42 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545692</v>
+        <v>545679</v>
       </c>
       <c r="R7" t="n">
-        <v>6522648</v>
+        <v>6522615</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1283,7 +1279,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298795</v>
+        <v>123298791</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,38 +1309,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545679</v>
+        <v>545692</v>
       </c>
       <c r="R8" t="n">
-        <v>6522615</v>
+        <v>6522648</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,6 +1385,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326310</v>
+        <v>123326129</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,39 +1642,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545680</v>
+        <v>545596</v>
       </c>
       <c r="R11" t="n">
-        <v>6522666</v>
+        <v>6522617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326129</v>
+        <v>123326310</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,30 +1748,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545596</v>
+        <v>545680</v>
       </c>
       <c r="R12" t="n">
-        <v>6522617</v>
+        <v>6522666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298798</v>
+        <v>123298790</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>91678</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545584</v>
+        <v>545705</v>
       </c>
       <c r="R2" t="n">
-        <v>6522641</v>
+        <v>6522653</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298793</v>
+        <v>123298795</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545664</v>
+        <v>545679</v>
       </c>
       <c r="R3" t="n">
-        <v>6522623</v>
+        <v>6522615</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -859,18 +855,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298790</v>
+        <v>123298798</v>
       </c>
       <c r="B4" t="n">
-        <v>91678</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545705</v>
+        <v>545584</v>
       </c>
       <c r="R4" t="n">
-        <v>6522653</v>
+        <v>6522641</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298797</v>
+        <v>123298793</v>
       </c>
       <c r="B5" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545605</v>
+        <v>545664</v>
       </c>
       <c r="R5" t="n">
-        <v>6522652</v>
+        <v>6522623</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1069,12 +1063,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298799</v>
+        <v>123298791</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1105,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545593</v>
+        <v>545692</v>
       </c>
       <c r="R6" t="n">
-        <v>6522623</v>
+        <v>6522648</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1177,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298795</v>
+        <v>123298797</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>92271</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545679</v>
+        <v>545605</v>
       </c>
       <c r="R7" t="n">
-        <v>6522615</v>
+        <v>6522652</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298791</v>
+        <v>123298799</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,42 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545692</v>
+        <v>545593</v>
       </c>
       <c r="R8" t="n">
-        <v>6522648</v>
+        <v>6522623</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1385,7 +1386,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123326307</v>
+        <v>123326300</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,39 +1416,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1456,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545693</v>
+        <v>545678</v>
       </c>
       <c r="R9" t="n">
-        <v>6522649</v>
+        <v>6522628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,11 +1483,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1510,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123326300</v>
+        <v>123326129</v>
       </c>
       <c r="B10" t="n">
         <v>90990</v>
@@ -1567,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545678</v>
+        <v>545596</v>
       </c>
       <c r="R10" t="n">
-        <v>6522628</v>
+        <v>6522617</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326129</v>
+        <v>123326307</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,30 +1628,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545596</v>
+        <v>545693</v>
       </c>
       <c r="R11" t="n">
-        <v>6522617</v>
+        <v>6522649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,7 +1739,7 @@
         <v>123326310</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>123326291</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298790</v>
+        <v>123298797</v>
       </c>
       <c r="B2" t="n">
-        <v>91678</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545705</v>
+        <v>545605</v>
       </c>
       <c r="R2" t="n">
-        <v>6522653</v>
+        <v>6522652</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298798</v>
+        <v>123298793</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545584</v>
+        <v>545664</v>
       </c>
       <c r="R4" t="n">
-        <v>6522641</v>
+        <v>6522623</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -957,12 +961,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298793</v>
+        <v>123298799</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,39 +1003,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545664</v>
+        <v>545593</v>
       </c>
       <c r="R5" t="n">
         <v>6522623</v>
@@ -1063,18 +1069,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298791</v>
+        <v>123298790</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>91678</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,42 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545692</v>
+        <v>545705</v>
       </c>
       <c r="R6" t="n">
-        <v>6522648</v>
+        <v>6522653</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1181,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298797</v>
+        <v>123298798</v>
       </c>
       <c r="B7" t="n">
-        <v>92271</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545605</v>
+        <v>545584</v>
       </c>
       <c r="R7" t="n">
-        <v>6522652</v>
+        <v>6522641</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298799</v>
+        <v>123298791</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,38 +1309,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545593</v>
+        <v>545692</v>
       </c>
       <c r="R8" t="n">
-        <v>6522623</v>
+        <v>6522648</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,6 +1385,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123326300</v>
+        <v>123326291</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,30 +1416,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1447,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545678</v>
+        <v>545653</v>
       </c>
       <c r="R9" t="n">
-        <v>6522628</v>
+        <v>6522620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,6 +1492,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123326129</v>
+        <v>123326310</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,30 +1536,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1553,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545596</v>
+        <v>545680</v>
       </c>
       <c r="R10" t="n">
-        <v>6522617</v>
+        <v>6522666</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326310</v>
+        <v>123326129</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,39 +1771,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545680</v>
+        <v>545596</v>
       </c>
       <c r="R12" t="n">
-        <v>6522666</v>
+        <v>6522617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326291</v>
+        <v>123326300</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,39 +1877,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1903,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545653</v>
+        <v>545678</v>
       </c>
       <c r="R13" t="n">
-        <v>6522620</v>
+        <v>6522628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,11 +1944,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,7 +1971,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123299964</v>
+        <v>123298794</v>
       </c>
       <c r="B14" t="n">
         <v>56700</v>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545682</v>
+        <v>545664</v>
       </c>
       <c r="R14" t="n">
-        <v>6522616</v>
+        <v>6522623</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298794</v>
+        <v>123299964</v>
       </c>
       <c r="B15" t="n">
         <v>56700</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545664</v>
+        <v>545682</v>
       </c>
       <c r="R15" t="n">
-        <v>6522623</v>
+        <v>6522616</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298795</v>
+        <v>123298799</v>
       </c>
       <c r="B3" t="n">
         <v>90990</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545679</v>
+        <v>545593</v>
       </c>
       <c r="R3" t="n">
-        <v>6522615</v>
+        <v>6522623</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298793</v>
+        <v>123298798</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545664</v>
+        <v>545584</v>
       </c>
       <c r="R4" t="n">
-        <v>6522623</v>
+        <v>6522641</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -961,18 +957,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298799</v>
+        <v>123298793</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,35 +993,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545593</v>
+        <v>545664</v>
       </c>
       <c r="R5" t="n">
         <v>6522623</v>
@@ -1069,12 +1063,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298790</v>
+        <v>123298795</v>
       </c>
       <c r="B6" t="n">
-        <v>91678</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545705</v>
+        <v>545679</v>
       </c>
       <c r="R6" t="n">
-        <v>6522653</v>
+        <v>6522615</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298798</v>
+        <v>123298791</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1207,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545584</v>
+        <v>545692</v>
       </c>
       <c r="R7" t="n">
-        <v>6522641</v>
+        <v>6522648</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1279,6 +1283,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298791</v>
+        <v>123298790</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>91678</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,42 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545692</v>
+        <v>545705</v>
       </c>
       <c r="R8" t="n">
-        <v>6522648</v>
+        <v>6522653</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1385,7 +1386,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123326291</v>
+        <v>123326310</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545653</v>
+        <v>545680</v>
       </c>
       <c r="R9" t="n">
-        <v>6522620</v>
+        <v>6522666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,11 +1492,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123326310</v>
+        <v>123326300</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,39 +1531,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1576,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545680</v>
+        <v>545678</v>
       </c>
       <c r="R10" t="n">
-        <v>6522666</v>
+        <v>6522628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1865,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326300</v>
+        <v>123326291</v>
       </c>
       <c r="B13" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,30 +1863,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1908,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545678</v>
+        <v>545653</v>
       </c>
       <c r="R13" t="n">
-        <v>6522628</v>
+        <v>6522620</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,6 +1939,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,7 +1971,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298794</v>
+        <v>123299964</v>
       </c>
       <c r="B14" t="n">
         <v>56700</v>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545664</v>
+        <v>545682</v>
       </c>
       <c r="R14" t="n">
-        <v>6522623</v>
+        <v>6522616</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123299964</v>
+        <v>123298794</v>
       </c>
       <c r="B15" t="n">
         <v>56700</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545682</v>
+        <v>545664</v>
       </c>
       <c r="R15" t="n">
-        <v>6522616</v>
+        <v>6522623</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298797</v>
+        <v>123298793</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545605</v>
+        <v>545664</v>
       </c>
       <c r="R2" t="n">
-        <v>6522652</v>
+        <v>6522623</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,12 +757,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Många blomställningar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298799</v>
+        <v>123298795</v>
       </c>
       <c r="B3" t="n">
         <v>90990</v>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545593</v>
+        <v>545679</v>
       </c>
       <c r="R3" t="n">
-        <v>6522623</v>
+        <v>6522615</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298798</v>
+        <v>123298791</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +901,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545584</v>
+        <v>545692</v>
       </c>
       <c r="R4" t="n">
-        <v>6522641</v>
+        <v>6522648</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -963,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298793</v>
+        <v>123298798</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,42 +1008,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545664</v>
+        <v>545584</v>
       </c>
       <c r="R5" t="n">
-        <v>6522623</v>
+        <v>6522641</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,18 +1074,12 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Många blomställningar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298795</v>
+        <v>123298799</v>
       </c>
       <c r="B6" t="n">
         <v>90990</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545679</v>
+        <v>545593</v>
       </c>
       <c r="R6" t="n">
-        <v>6522615</v>
+        <v>6522623</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298791</v>
+        <v>123298790</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>91678</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,42 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Visjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545692</v>
+        <v>545705</v>
       </c>
       <c r="R7" t="n">
-        <v>6522648</v>
+        <v>6522653</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1283,7 +1284,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298790</v>
+        <v>123298797</v>
       </c>
       <c r="B8" t="n">
-        <v>91678</v>
+        <v>92271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545705</v>
+        <v>545605</v>
       </c>
       <c r="R8" t="n">
-        <v>6522653</v>
+        <v>6522652</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123326310</v>
+        <v>123326291</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545680</v>
+        <v>545653</v>
       </c>
       <c r="R9" t="n">
-        <v>6522666</v>
+        <v>6522620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,6 +1492,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326307</v>
+        <v>123326129</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,39 +1642,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1677,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545693</v>
+        <v>545596</v>
       </c>
       <c r="R11" t="n">
-        <v>6522649</v>
+        <v>6522617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123326129</v>
+        <v>123326310</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,30 +1748,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545596</v>
+        <v>545680</v>
       </c>
       <c r="R12" t="n">
-        <v>6522617</v>
+        <v>6522666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326291</v>
+        <v>123326307</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545653</v>
+        <v>545693</v>
       </c>
       <c r="R13" t="n">
-        <v>6522620</v>
+        <v>6522649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,7 +1971,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123299964</v>
+        <v>123298794</v>
       </c>
       <c r="B14" t="n">
         <v>56700</v>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545682</v>
+        <v>545664</v>
       </c>
       <c r="R14" t="n">
-        <v>6522616</v>
+        <v>6522623</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298794</v>
+        <v>123299964</v>
       </c>
       <c r="B15" t="n">
         <v>56700</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545664</v>
+        <v>545682</v>
       </c>
       <c r="R15" t="n">
-        <v>6522623</v>
+        <v>6522616</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 5346-2025 artfynd.xlsx
+++ b/artfynd/A 5346-2025 artfynd.xlsx
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123326300</v>
+        <v>123326129</v>
       </c>
       <c r="B10" t="n">
         <v>90990</v>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545678</v>
+        <v>545596</v>
       </c>
       <c r="R10" t="n">
-        <v>6522628</v>
+        <v>6522617</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123326129</v>
+        <v>123326307</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,30 +1642,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1673,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545596</v>
+        <v>545693</v>
       </c>
       <c r="R11" t="n">
-        <v>6522617</v>
+        <v>6522649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1718,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123326307</v>
+        <v>123326300</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,39 +1877,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1903,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545693</v>
+        <v>545678</v>
       </c>
       <c r="R13" t="n">
-        <v>6522649</v>
+        <v>6522628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,11 +1944,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD13" t="b">
